--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Brice est près de la porte. Maman lace ses chaussures. Maman dit : on va au jardin. Avant de sortir, Brice prend son manteau. Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse. Maman dit : on rentre. Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard, maman dit : on va à la boulangerie. Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie. Maman dit : merci Brice.</t>
+          <t>Brice est près de la porte. Maman lace ses chaussures. On va au jardin. Avant de sortir, Brice prend son manteau. Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse. On rentre. Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard, On va à la boulangerie. Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie. Merci Brice.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Brice est près de la porte. Maman lace ses chaussures.
+maman|On va au jardin. Avant de sortir, Brice prend son manteau.
+narrateur|Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse.
+maman|On rentre.
+narrateur|Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard,
+maman|On va à la boulangerie.
+narrateur|Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie.
+maman|Merci Brice.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Avant de sortir, que prend Brice ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Brice a pris le manteau. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1837,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Brice pose les chaussures. Le manteau reste au crochet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2004,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2044,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 maman|Merci Brice.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Avant de sortir, que prend Brice ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Brice a pris le manteau. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1842,6 +1850,7 @@
           <t>narrateur|Brice pose les chaussures. Le manteau reste au crochet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2009,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2252,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brice prend son manteau, deux sorties</t>
+          <t>Nino, le jardin puis le pain</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino sort deux fois : jardin, puis boulangerie. Chaque fois il prend le manteau gris et le raccroche.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Brice est près de la porte. Maman lace ses chaussures. On va au jardin. Avant de sortir, Brice prend son manteau. Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse. On rentre. Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard, On va à la boulangerie. Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie. Merci Brice.</t>
+          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino est près de la porte. Son manteau gris attend au crochet. On va d'abord au jardin. Avant de sortir, on prend le manteau. Nino prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. On rentre ? Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Bravo. En rentrant, on le pose. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. Bravo. Tu as fait du bon travail. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Même leçon, autre sortie. Manteau pour sortir. Manteau à sa place en rentrant. Deux fois, maman. Oui. Deux fois. Merci, Nino.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Brice est près de la porte. Maman lace ses chaussures.
-maman|On va au jardin. Avant de sortir, Brice prend son manteau.
-narrateur|Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse.
-maman|On rentre.
-narrateur|Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard,
+          <t>narrateur|Un sac à pain vide pend à une chaise.
+narrateur|Des miettes dorment sur la planche.
+narrateur|L'horloge de la cuisine avance doucement.
+narrateur|Une mouche marche sur la vitre.
+narrateur|Maman s'essuie les mains dans un torchon.
+maman|Nino, tu as vu le sac vide ?
+enfant-m|Oui. Il n'y a plus de pain.
+narrateur|En ce moment, Nino est près de la porte.
+narrateur|Son manteau gris attend au crochet.
+maman|On va d'abord au jardin.
+maman|Avant de sortir, on prend le manteau.
+narrateur|Nino prend le manteau gris.
+narrateur|Il est un peu épais.
+narrateur|Nino glisse un bras, puis l'autre.
+maman|Bravo. Tu as pris ton manteau.
+narrateur|Maman lace les chaussures.
+narrateur|Ils vont au jardin.
+narrateur|L'air est frais.
+narrateur|Nino touche une feuille lisse.
+enfant-m|Elle est froide, maman.
+maman|Oui. L'air est frais.
+maman|On rentre ?
+narrateur|Nino entre.
+narrateur|Il retire le manteau.
+narrateur|Il le raccroche au crochet.
+narrateur|Le manteau gris est à sa place.
+maman|Bravo. En rentrant, on le pose.
+narrateur|Plus tard, maman prend le sac vide.
 maman|On va à la boulangerie.
-narrateur|Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie.
-maman|Merci Brice.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nino se souvient.
+narrateur|Avant de sortir, il prend le manteau.
+narrateur|Le même manteau gris.
+maman|Tu t'es souvenu tout seul.
+maman|Bravo. Tu as fait du bon travail.
+narrateur|À la boulangerie, ça sent le pain chaud.
+narrateur|La vitrine est un peu embuée.
+enfant-m|Le pain est doré.
+maman|Oui. On en prend un.
+narrateur|Maman glisse le pain dans le sac.
+narrateur|Puis ils rentrent.
+narrateur|Nino raccroche encore le manteau.
+narrateur|Le crochet fait le même petit bruit.
+maman|Même leçon, autre sortie.
+maman|Manteau pour sortir. Manteau à sa place en rentrant.
+enfant-m|Deux fois, maman.
+maman|Oui. Deux fois. Merci, Nino.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>horloge,porte</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avant de sortir, que prend Brice ?</t>
+          <t>Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1561,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Avant de sortir, que prend Brice ?</t>
+          <t>narrateur|Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Brice a pris le manteau. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché.</t>
+          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Deux fois aussi. Bravo. Tu t'es souvenu. Avant de sortir, le manteau. En rentrant, on le pose. Il est au crochet. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1733,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Brice a pris le manteau. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché.</t>
+          <t>narrateur|Nino a pris le manteau.
+narrateur|Au jardin, puis à la boulangerie.
+narrateur|Deux sorties. Le même manteau gris.
+narrateur|En rentrant, il l'a raccroché.
+narrateur|Deux fois aussi.
+maman|Bravo. Tu t'es souvenu.
+maman|Avant de sortir, le manteau.
+maman|En rentrant, on le pose.
+enfant-m|Il est au crochet.
+maman|Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Brice pose les chaussures. Le manteau reste au crochet.</t>
+          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui. Bravo, Nino.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1847,7 +1910,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Brice pose les chaussures. Le manteau reste au crochet.</t>
+          <t>narrateur|Nino pose les chaussures.
+narrateur|Le manteau reste au crochet.
+narrateur|Maman pose le pain sur la planche.
+maman|Tu as fini de poser tes chaussures ?
+enfant-m|Oui, maman.
+narrateur|Le sac n'est plus vide.
+narrateur|Les miettes nouvelles sentent le chaud.
+maman|On a le pain, maintenant.
+enfant-m|Et le manteau est à sa place.
+maman|Oui. Bravo, Nino.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1875,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Tu as fait du bon travail. Le pain doré attend sur la planche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2015,7 +2087,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai pris le manteau deux fois.
+enfant-m|Jardin, puis boulangerie.
+maman|Et tu l'as raccroché.
+maman|Bravo, Nino. Tu as fait du bon travail.
+narrateur|Le pain doré attend sur la planche.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2037,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino est près de la porte. Son manteau gris attend au crochet. On va d'abord au jardin. Avant de sortir, on prend le manteau. Nino prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. On rentre ? Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Bravo. En rentrant, on le pose. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. Bravo. Tu as fait du bon travail. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Même leçon, autre sortie. Manteau pour sortir. Manteau à sa place en rentrant. Deux fois, maman. Oui. Deux fois. Merci, Nino.</t>
+          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. On va d'abord au jardin. Avant de sortir, on prend le manteau. Nino prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Bravo. En rentrant, on le pose. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. Bravo. Tu as fait du bon travail. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Au jardin, puis à la boulangerie. Chaque fois, le manteau. Chaque fois, on le pose. Deux fois, maman. Oui. Deux fois. Merci, Nino. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
 narrateur|Maman s'essuie les mains dans un torchon.
 maman|Nino, tu as vu le sac vide ?
 enfant-m|Oui. Il n'y a plus de pain.
-narrateur|En ce moment, Nino est près de la porte.
+narrateur|En ce moment, Nino souffle sur les miettes.
 narrateur|Son manteau gris attend au crochet.
 maman|On va d'abord au jardin.
 maman|Avant de sortir, on prend le manteau.
@@ -1345,7 +1345,9 @@
 narrateur|Nino touche une feuille lisse.
 enfant-m|Elle est froide, maman.
 maman|Oui. L'air est frais.
-maman|On rentre ?
+narrateur|Un oiseau picore près de la haie.
+narrateur|Nino l'écoute un moment.
+maman|C'est l'heure de rentrer.
 narrateur|Nino entre.
 narrateur|Il retire le manteau.
 narrateur|Il le raccroche au crochet.
@@ -1366,10 +1368,15 @@
 narrateur|Puis ils rentrent.
 narrateur|Nino raccroche encore le manteau.
 narrateur|Le crochet fait le même petit bruit.
-maman|Même leçon, autre sortie.
-maman|Manteau pour sortir. Manteau à sa place en rentrant.
+maman|Au jardin, puis à la boulangerie.
+maman|Chaque fois, le manteau. Chaque fois, on le pose.
 enfant-m|Deux fois, maman.
-maman|Oui. Deux fois. Merci, Nino.</t>
+maman|Oui. Deux fois. Merci, Nino.
+narrateur|Nino pose le sac à pain sur la chaise.
+narrateur|Le pain est encore un peu chaud.
+maman|Tu as fini de poser le sac ?
+enfant-m|Oui, maman.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -2114,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2164,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino, le jardin puis le pain</t>
+          <t>Le sac à pain de Nino</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino sort deux fois : jardin, puis boulangerie. Chaque fois il prend le manteau gris et le raccroche.</t>
+          <t>Le sac à pain est vide. Nino veut un pain doré. D'abord un tour au jardin : oiseau, feuille froide. Le manteau gris au crochet. Le sac vide pendait sur le manteau. À la boulangerie il se souvient. Le pain rentre chaud.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. On va d'abord au jardin. Avant de sortir, on prend le manteau. Nino prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Bravo. Tu as pris ton manteau. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Bravo. En rentrant, on le pose. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. Bravo. Tu as fait du bon travail. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Au jardin, puis à la boulangerie. Chaque fois, le manteau. Chaque fois, on le pose. Deux fois, maman. Oui. Deux fois. Merci, Nino. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman. Bravo.</t>
+          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. L'horloge dit qu'il est tôt. On va d'abord au jardin. On verra si l'oiseau est là. Nino va vers le crochet. Le sac vide pendait aussi au crochet. Il cache un peu le manteau. Le sac est devant. Enlève le sac d'abord. Puis le manteau. Nino pose le sac sur la chaise. Il prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Tu as pris ton manteau ? Oui, maman. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. Tu as vu l'oiseau ? Oui. Il picore. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Deux fois, maman. Oui. Deux fois. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice est près de la porte. Maman lace ses chaussures. Maman dit : on va au jardin. Avant de sortir, Brice prend son &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt;. Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse. Maman dit : on rentre. Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard, maman dit : on va à la boulangerie. Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie. Maman dit : merci Brice.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. L'horloge dit qu'il est tôt. On va d'abord au jardin. On verra si l'oiseau est là. Nino va vers le crochet. Le sac vide pendait aussi au crochet. Il cache un peu le manteau. Le sac est devant. Enlève le sac d'abord. Puis le manteau. Nino pose le sac sur la chaise. Il prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Tu as pris ton manteau ? Oui, maman. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. Tu as vu l'oiseau ? Oui. Il picore. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Deux fois, maman. Oui. Deux fois. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1330,53 +1330,64 @@
 narrateur|Une mouche marche sur la vitre.
 narrateur|Maman s'essuie les mains dans un torchon.
 maman|Nino, tu as vu le sac vide ?
-enfant-m|Oui. Il n'y a plus de pain.
+enfant-m|Oui.
+enfant-m|Il n'y a plus de pain.
 narrateur|En ce moment, Nino souffle sur les miettes.
 narrateur|Son manteau gris attend au crochet.
+maman|L'horloge dit qu'il est tôt.
 maman|On va d'abord au jardin.
-maman|Avant de sortir, on prend le manteau.
-narrateur|Nino prend le manteau gris.
+maman|On verra si l'oiseau est là.
+narrateur|Nino va vers le crochet.
+narrateur|Le sac vide pendait aussi au crochet.
+narrateur|Il cache un peu le manteau.
+enfant-m|Le sac est devant.
+maman|Enlève le sac d'abord.
+maman|Puis le manteau.
+narrateur|Nino pose le sac sur la chaise.
+narrateur|Il prend le manteau gris.
 narrateur|Il est un peu épais.
 narrateur|Nino glisse un bras, puis l'autre.
-maman|Bravo. Tu as pris ton manteau.
+maman|Tu as pris ton manteau ?
+enfant-m|Oui, maman.
 narrateur|Maman lace les chaussures.
 narrateur|Ils vont au jardin.
 narrateur|L'air est frais.
 narrateur|Nino touche une feuille lisse.
 enfant-m|Elle est froide, maman.
-maman|Oui. L'air est frais.
+maman|Oui.
+maman|L'air est frais.
 narrateur|Un oiseau picore près de la haie.
 narrateur|Nino l'écoute un moment.
+maman|Tu as vu l'oiseau ?
+enfant-m|Oui.
+enfant-m|Il picore.
 maman|C'est l'heure de rentrer.
 narrateur|Nino entre.
 narrateur|Il retire le manteau.
 narrateur|Il le raccroche au crochet.
 narrateur|Le manteau gris est à sa place.
-maman|Bravo. En rentrant, on le pose.
 narrateur|Plus tard, maman prend le sac vide.
 maman|On va à la boulangerie.
 narrateur|Nino se souvient.
 narrateur|Avant de sortir, il prend le manteau.
 narrateur|Le même manteau gris.
 maman|Tu t'es souvenu tout seul.
-maman|Bravo. Tu as fait du bon travail.
 narrateur|À la boulangerie, ça sent le pain chaud.
 narrateur|La vitrine est un peu embuée.
 enfant-m|Le pain est doré.
-maman|Oui. On en prend un.
+maman|Oui.
+maman|On en prend un.
 narrateur|Maman glisse le pain dans le sac.
 narrateur|Puis ils rentrent.
 narrateur|Nino raccroche encore le manteau.
 narrateur|Le crochet fait le même petit bruit.
-maman|Au jardin, puis à la boulangerie.
-maman|Chaque fois, le manteau. Chaque fois, on le pose.
 enfant-m|Deux fois, maman.
-maman|Oui. Deux fois. Merci, Nino.
+maman|Oui.
+maman|Deux fois.
 narrateur|Nino pose le sac à pain sur la chaise.
 narrateur|Le pain est encore un peu chaud.
 maman|Tu as fini de poser le sac ?
-enfant-m|Oui, maman.
-maman|Bravo.</t>
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1413,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Avant de &lt;emphasis level="moderate"&gt;sortir&lt;/emphasis&gt;, que prend Brice ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1443,7 +1454,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il prend le manteau. Que prend Brice ?</t>
+          <t>Il prend le manteau. Que prend Nino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1485,14 +1496,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1571,7 +1582,6 @@
           <t>narrateur|Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Deux fois aussi. Bravo. Tu t'es souvenu. Avant de sortir, le manteau. En rentrant, on le pose. Il est au crochet. Oui. C'est du bon travail.</t>
+          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Tu t'es souvenu. Il est au crochet. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice a pris le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt;. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Tu t'es souvenu. Il est au crochet. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1664,7 +1674,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1742,17 +1752,14 @@
         <is>
           <t>narrateur|Nino a pris le manteau.
 narrateur|Au jardin, puis à la boulangerie.
-narrateur|Deux sorties. Le même manteau gris.
+narrateur|Deux sorties.
+narrateur|Le même manteau gris.
 narrateur|En rentrant, il l'a raccroché.
-narrateur|Deux fois aussi.
-maman|Bravo. Tu t'es souvenu.
-maman|Avant de sortir, le manteau.
-maman|En rentrant, on le pose.
+maman|Tu t'es souvenu.
 enfant-m|Il est au crochet.
-maman|Oui. C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui. Bravo, Nino.</t>
+          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Brice pose les chaussures. Le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt; reste au crochet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1845,7 +1852,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1926,10 +1933,9 @@
 narrateur|Les miettes nouvelles sentent le chaud.
 maman|On a le pain, maintenant.
 enfant-m|Et le manteau est à sa place.
-maman|Oui. Bravo, Nino.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,7 +1965,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Tu as fait du bon travail. Le pain doré attend sur la planche. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2022,7 +2028,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2097,12 +2103,12 @@
           <t>enfant-m|J'ai pris le manteau deux fois.
 enfant-m|Jardin, puis boulangerie.
 maman|Et tu l'as raccroché.
-maman|Bravo, Nino. Tu as fait du bon travail.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
 narrateur|Le pain doré attend sur la planche.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2121,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2201,6 +2207,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -1960,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Tu as fait du bon travail. Le pain doré attend sur la planche. L'histoire est finie.</t>
+          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Le pain doré attend sur la planche.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Tu as fait du bon travail. Le pain doré attend sur la planche. L'histoire est finie.</t>
+          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Le pain doré attend sur la planche.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,9 +2104,7 @@
 enfant-m|Jardin, puis boulangerie.
 maman|Et tu l'as raccroché.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
-narrateur|Le pain doré attend sur la planche.
-narrateur|L'histoire est finie.</t>
+narrateur|Le pain doré attend sur la planche.</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2210,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison, jardin puis boulangerie</t>
+          <t>cuisine, jardin, boulangerie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brice, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
+++ b/stories/arbres/ATOM-AUT.AFF.002-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Le sac à pain est vide. Nino veut un pain doré. D'abord un tour au jardin : oiseau, feuille froide. Le manteau gris au crochet. Le sac vide pendait sur le manteau. À la boulangerie il se souvient. Le pain rentre chaud.</t>
+          <t>Le tic de l'horloge répond dans le cuivre. Un éclat d'horloge cligne sur le sac à pain vide. Nino veut le pain du fournil, maintenant. Il court sans manteau : le sac accroche le crochet, tombe. Il refuse de forcer, enfile le gris, passe au thym. Au fournil, il pousse trop vite. Il refuse de foncer, retrouve l'éclat sur la croûte. Le sac paie le début.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. L'horloge dit qu'il est tôt. On va d'abord au jardin. On verra si l'oiseau est là. Nino va vers le crochet. Le sac vide pendait aussi au crochet. Il cache un peu le manteau. Le sac est devant. Enlève le sac d'abord. Puis le manteau. Nino pose le sac sur la chaise. Il prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Tu as pris ton manteau ? Oui, maman. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. Tu as vu l'oiseau ? Oui. Il picore. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Deux fois, maman. Oui. Deux fois. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman.</t>
+          <t>Le tic de l'horloge répond dans le cuivre de la casserole. La casserole est vide, froide sous le doigt. Nino connaît cette cuisine, ses recoins. Un filet de farine dessine un chemin sur la table. Sur la chaise, un sac à pain pend, vide. Le lin du sac sent la farine sèche. Un éclat d'horloge cligne sur le lin. Nino ne sait pas à quoi il servira. Maman plie le torchon, près de la planche. Le torchon sent le levain. La porte du jardin laisse un filet d'air. Ça sent le fournil du village. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. Je veux le pain, maintenant ! On y va, avec le sac. En ce moment, Nino saisit le sac vide. Le lin est rêche sous les doigts. Son manteau gris attend au crochet. Les pieds de Nino tapent le carrelage. Je sors, maman ! Nino court vers la porte du jardin. Il veut le pain, sans attendre. Le sac accroche le crochet, d'un coup. Oh. Nino tire plus fort. Le sac tombe, plat, sur le carrelage. Ça reste coincé ! La sangle reste tordue, près du crochet. Le manteau gris n'a pas bougé. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'air du jardin pique les poignets, sans manteau. Maman se baisse à sa hauteur. Tu regardes le crochet ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un sac à pain vide pend à une chaise. Des miettes dorment sur la planche. L'horloge de la cuisine avance doucement. Une mouche marche sur la vitre. Maman s'essuie les mains dans un torchon. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. En ce moment, Nino souffle sur les miettes. Son manteau gris attend au crochet. L'horloge dit qu'il est tôt. On va d'abord au jardin. On verra si l'oiseau est là. Nino va vers le crochet. Le sac vide pendait aussi au crochet. Il cache un peu le manteau. Le sac est devant. Enlève le sac d'abord. Puis le manteau. Nino pose le sac sur la chaise. Il prend le manteau gris. Il est un peu épais. Nino glisse un bras, puis l'autre. Tu as pris ton manteau ? Oui, maman. Maman lace les chaussures. Ils vont au jardin. L'air est frais. Nino touche une feuille lisse. Elle est froide, maman. Oui. L'air est frais. Un oiseau picore près de la haie. Nino l'écoute un moment. Tu as vu l'oiseau ? Oui. Il picore. C'est l'heure de rentrer. Nino entre. Il retire le manteau. Il le raccroche au crochet. Le manteau gris est à sa place. Plus tard, maman prend le sac vide. On va à la boulangerie. Nino se souvient. Avant de sortir, il prend le manteau. Le même manteau gris. Tu t'es souvenu tout seul. À la boulangerie, ça sent le pain chaud. La vitrine est un peu embuée. Le pain est doré. Oui. On en prend un. Maman glisse le pain dans le sac. Puis ils rentrent. Nino raccroche encore le manteau. Le crochet fait le même petit bruit. Deux fois, maman. Oui. Deux fois. Nino pose le sac à pain sur la chaise. Le pain est encore un peu chaud. Tu as fini de poser le sac ? Oui, maman.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le tic de l'horloge répond dans le cuivre de la casserole. La casserole est vide, froide sous le doigt. Nino connaît cette cuisine, ses recoins. Un filet de farine dessine un chemin sur la table. Sur la chaise, un sac à pain pend, vide. Le lin du sac sent la farine sèche. Un &lt;emphasis level="moderate"&gt;éclat d'horloge&lt;/emphasis&gt; cligne sur le lin. Nino ne sait pas à quoi il servira. Maman plie le torchon, près de la planche. Le torchon sent le levain. La porte du jardin laisse un filet d'air. Ça sent le fournil du village. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. Je veux le pain, maintenant ! On y va, avec le sac. En ce moment, Nino saisit le sac vide. Le lin est rêche sous les doigts. Son manteau gris attend au crochet. Les pieds de Nino tapent le carrelage. Je sors, maman ! Nino court vers la porte du jardin. Il veut le pain, sans attendre. Le sac accroche le crochet, d'un coup. Oh. Nino tire plus fort. Le sac tombe, plat, sur le carrelage. Ça reste coincé ! La sangle reste tordue, près du crochet. Le manteau gris n'a pas bougé. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'air du jardin pique les poignets, sans manteau. Maman se baisse à sa hauteur. Tu regardes le crochet ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Brice est près de la porte. Maman lace ses chaussures. Maman dit : on va au jardin. Avant de sortir, Brice prend son &lt;emphasis&gt;manteau&lt;/emphasis&gt;. Le manteau est gris. Il est un peu épais. Brice glisse un bras, puis l'autre. Ils vont au jardin. L'air est frais. Brice touche une feuille lisse. Maman dit : on rentre. Brice entre. Il retire le manteau. Il le raccroche au crochet. Le manteau est à sa place. Plus tard, maman dit : on va à la boulangerie. Brice se souvient. Avant de sortir, il prend le manteau. À la boulangerie, ça sent le pain. Puis ils rentrent. Brice raccroche encore le manteau. Même leçon, autre sortie. Maman dit : merci Brice. [pause]</t>
+          <t>Le tic de l'horloge répond dans le cuivre de la casserole. La casserole est vide, froide sous le doigt. Nino connaît cette cuisine, ses recoins. Un filet de farine dessine un chemin sur la table. Sur la chaise, un sac à pain pend, vide. Le lin du sac sent la farine sèche. Un &lt;emphasis&gt;éclat d'horloge&lt;/emphasis&gt; cligne sur le lin. Nino ne sait pas à quoi il servira. Maman plie le torchon, près de la planche. Le torchon sent le levain. La porte du jardin laisse un filet d'air. Ça sent le fournil du village. Nino, tu as vu le sac vide ? Oui. Il n'y a plus de pain. Je veux le pain, maintenant ! On y va, avec le sac. En ce moment, Nino saisit le sac vide. Le lin est rêche sous les doigts. Son manteau gris attend au crochet. Les pieds de Nino tapent le carrelage. Je sors, maman ! Nino court vers la porte du jardin. Il veut le pain, sans attendre. Le sac accroche le crochet, d'un coup. Oh. Nino tire plus fort. Le sac tombe, plat, sur le carrelage. Ça reste coincé ! La sangle reste tordue, près du crochet. Le manteau gris n'a pas bougé. Le sourire de Nino disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. L'air du jardin pique les poignets, sans manteau. Maman se baisse à sa hauteur. Tu regardes le crochet ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>manteau</t>
+          <t>éclat d'horloge</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,78 +1321,54 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_le_pain_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un sac à pain vide pend à une chaise.
-narrateur|Des miettes dorment sur la planche.
-narrateur|L'horloge de la cuisine avance doucement.
-narrateur|Une mouche marche sur la vitre.
-narrateur|Maman s'essuie les mains dans un torchon.
+          <t>narrateur|Le tic de l'horloge répond dans le cuivre de la casserole.
+narrateur|La casserole est vide, froide sous le doigt.
+narrateur|Nino connaît cette cuisine, ses recoins.
+narrateur|Un filet de farine dessine un chemin sur la table.
+narrateur|Sur la chaise, un sac à pain pend, vide.
+narrateur|Le lin du sac sent la farine sèche.
+narrateur|Un éclat d'horloge cligne sur le lin.
+narrateur|Nino ne sait pas à quoi il servira.
+narrateur|Maman plie le torchon, près de la planche.
+narrateur|Le torchon sent le levain.
+narrateur|La porte du jardin laisse un filet d'air.
+narrateur|Ça sent le fournil du village.
 maman|Nino, tu as vu le sac vide ?
 enfant-m|Oui.
 enfant-m|Il n'y a plus de pain.
-narrateur|En ce moment, Nino souffle sur les miettes.
+enfant-m|Je veux le pain, maintenant !
+maman|On y va, avec le sac.
+narrateur|En ce moment, Nino saisit le sac vide.
+narrateur|Le lin est rêche sous les doigts.
 narrateur|Son manteau gris attend au crochet.
-maman|L'horloge dit qu'il est tôt.
-maman|On va d'abord au jardin.
-maman|On verra si l'oiseau est là.
-narrateur|Nino va vers le crochet.
-narrateur|Le sac vide pendait aussi au crochet.
-narrateur|Il cache un peu le manteau.
-enfant-m|Le sac est devant.
-maman|Enlève le sac d'abord.
-maman|Puis le manteau.
-narrateur|Nino pose le sac sur la chaise.
-narrateur|Il prend le manteau gris.
-narrateur|Il est un peu épais.
-narrateur|Nino glisse un bras, puis l'autre.
-maman|Tu as pris ton manteau ?
-enfant-m|Oui, maman.
-narrateur|Maman lace les chaussures.
-narrateur|Ils vont au jardin.
-narrateur|L'air est frais.
-narrateur|Nino touche une feuille lisse.
-enfant-m|Elle est froide, maman.
-maman|Oui.
-maman|L'air est frais.
-narrateur|Un oiseau picore près de la haie.
-narrateur|Nino l'écoute un moment.
-maman|Tu as vu l'oiseau ?
-enfant-m|Oui.
-enfant-m|Il picore.
-maman|C'est l'heure de rentrer.
-narrateur|Nino entre.
-narrateur|Il retire le manteau.
-narrateur|Il le raccroche au crochet.
-narrateur|Le manteau gris est à sa place.
-narrateur|Plus tard, maman prend le sac vide.
-maman|On va à la boulangerie.
-narrateur|Nino se souvient.
-narrateur|Avant de sortir, il prend le manteau.
-narrateur|Le même manteau gris.
-maman|Tu t'es souvenu tout seul.
-narrateur|À la boulangerie, ça sent le pain chaud.
-narrateur|La vitrine est un peu embuée.
-enfant-m|Le pain est doré.
-maman|Oui.
-maman|On en prend un.
-narrateur|Maman glisse le pain dans le sac.
-narrateur|Puis ils rentrent.
-narrateur|Nino raccroche encore le manteau.
-narrateur|Le crochet fait le même petit bruit.
-enfant-m|Deux fois, maman.
-maman|Oui.
-maman|Deux fois.
-narrateur|Nino pose le sac à pain sur la chaise.
-narrateur|Le pain est encore un peu chaud.
-maman|Tu as fini de poser le sac ?
-enfant-m|Oui, maman.</t>
+narrateur|Les pieds de Nino tapent le carrelage.
+enfant-m|Je sors, maman !
+narrateur|Nino court vers la porte du jardin.
+narrateur|Il veut le pain, sans attendre.
+narrateur|Le sac accroche le crochet, d'un coup.
+enfant-m|Oh.
+narrateur|Nino tire plus fort.
+narrateur|Le sac tombe, plat, sur le carrelage.
+enfant-m|Ça reste coincé !
+narrateur|La sangle reste tordue, près du crochet.
+narrateur|Le manteau gris n'a pas bougé.
+narrateur|Le sourire de Nino disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|L'air du jardin pique les poignets, sans manteau.
+narrateur|Maman se baisse à sa hauteur.
+maman|Tu regardes le crochet ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>horloge,porte</t>
+          <t>horloge,casserole,porte</t>
         </is>
       </c>
     </row>
@@ -1419,17 +1395,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Avant de sortir, que prend Nino ?</t>
+          <t>Nino veut sortir. Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Avant de sortir, que prend Nino ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Nino veut &lt;emphasis level="moderate"&gt;sortir&lt;/emphasis&gt;. Avant de sortir, que prend Nino ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Avant de &lt;emphasis&gt;sortir&lt;/emphasis&gt;, que prend Brice ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Nino veut &lt;emphasis&gt;sortir&lt;/emphasis&gt;. Avant de sortir, que prend Nino ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1492,7 +1468,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1476,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1518,11 +1494,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1533,23 +1509,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1558,28 +1534,29 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=le_manteau_avant_la_porte; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Avant de sortir, que prend Nino ?</t>
+          <t>narrateur|Nino veut sortir.
+narrateur|Avant de sortir, que prend Nino ?</t>
         </is>
       </c>
     </row>
@@ -1606,17 +1583,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Tu t'es souvenu. Il est au crochet. Oui.</t>
+          <t>Nino refuse de tirer plus fort. Il pose un genou au carrelage. Le sac est plat, la sangle tordue. Je le pose. Il pose le sac sur la chaise. Le crochet montre le manteau gris. Tu le prends, Nino ? Oui, maman. Nino glisse un bras, puis l'autre. Le tissu est épais, un peu rêche. Les boutons sont froids sous le doigt. Merci, Nino. Le manteau est prêt ? Oui, maman. Maman lace les chaussures, sans se presser. On ouvre le jardin ? Oui. Ils passent la porte du jardin. L'air pique les joues, pas les poignets. J'ai chaud, maman. Tu le sens sur tes bras ? Oui. Un arrosoir goutte près du thym. Le thym sent fort, près de la grille. Il goutte, maman. Tu l'entends, Nino ? Nino écoute la goutte, un instant. La grille du jardin grince, un peu. On rentre. Nino entre. Il retire le manteau gris. Il le raccroche au crochet. Il est à sa place.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino a pris le manteau. Au jardin, puis à la boulangerie. Deux sorties. Le même manteau gris. En rentrant, il l'a raccroché. Tu t'es souvenu. Il est au crochet. Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino refuse de tirer plus fort. Il pose un genou au carrelage. Le sac est plat, la sangle tordue. Je le pose. Il pose le sac sur la chaise. Le crochet montre le &lt;emphasis level="moderate"&gt;manteau&lt;/emphasis&gt; gris. Tu le prends, Nino ? Oui, maman. Nino glisse un bras, puis l'autre. Le tissu est épais, un peu rêche. Les boutons sont froids sous le doigt. Merci, Nino. Le manteau est prêt ? Oui, maman. Maman lace les chaussures, sans se presser. On ouvre le jardin ? Oui. Ils passent la porte du jardin. L'air pique les joues, pas les poignets. J'ai chaud, maman. Tu le sens sur tes bras ? Oui. Un arrosoir goutte près du thym. Le thym sent fort, près de la grille. Il goutte, maman. Tu l'entends, Nino ? Nino écoute la goutte, un instant. La grille du jardin grince, un peu. On rentre. Nino entre. Il retire le manteau gris. Il le raccroche au crochet. Il est à sa place.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Brice a pris le &lt;emphasis&gt;manteau&lt;/emphasis&gt;. Au jardin, puis à la boulangerie. En rentrant, il l'a raccroché. [pause]</t>
+          <t>Nino refuse de tirer plus fort. Il pose un genou au carrelage. Le sac est plat, la sangle tordue. Je le pose. Il pose le sac sur la chaise. Le crochet montre le &lt;emphasis&gt;manteau&lt;/emphasis&gt; gris. Tu le prends, Nino ? Oui, maman. Nino glisse un bras, puis l'autre. Le tissu est épais, un peu rêche. Les boutons sont froids sous le doigt. Merci, Nino. Le manteau est prêt ? Oui, maman. Maman lace les chaussures, sans se presser. On ouvre le jardin ? Oui. Ils passent la porte du jardin. L'air pique les joues, pas les poignets. J'ai chaud, maman. Tu le sens sur tes bras ? Oui. Un arrosoir goutte près du thym. Le thym sent fort, près de la grille. Il goutte, maman. Tu l'entends, Nino ? Nino écoute la goutte, un instant. La grille du jardin grince, un peu. On rentre. Nino entre. Il retire le manteau gris. Il le raccroche au crochet. Il est à sa place. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1663,7 +1640,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1648,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1704,23 +1681,23 @@
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1729,10 +1706,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1745,19 +1722,49 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_prend_le_manteau_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino a pris le manteau.
-narrateur|Au jardin, puis à la boulangerie.
-narrateur|Deux sorties.
-narrateur|Le même manteau gris.
-narrateur|En rentrant, il l'a raccroché.
-maman|Tu t'es souvenu.
-enfant-m|Il est au crochet.
-maman|Oui.</t>
+          <t>narrateur|Nino refuse de tirer plus fort.
+narrateur|Il pose un genou au carrelage.
+narrateur|Le sac est plat, la sangle tordue.
+enfant-m|Je le pose.
+narrateur|Il pose le sac sur la chaise.
+narrateur|Le crochet montre le manteau gris.
+maman|Tu le prends, Nino ?
+enfant-m|Oui, maman.
+narrateur|Nino glisse un bras, puis l'autre.
+narrateur|Le tissu est épais, un peu rêche.
+narrateur|Les boutons sont froids sous le doigt.
+maman|Merci, Nino.
+maman|Le manteau est prêt ?
+enfant-m|Oui, maman.
+narrateur|Maman lace les chaussures, sans se presser.
+maman|On ouvre le jardin ?
+enfant-m|Oui.
+narrateur|Ils passent la porte du jardin.
+narrateur|L'air pique les joues, pas les poignets.
+enfant-m|J'ai chaud, maman.
+maman|Tu le sens sur tes bras ?
+enfant-m|Oui.
+narrateur|Un arrosoir goutte près du thym.
+narrateur|Le thym sent fort, près de la grille.
+enfant-m|Il goutte, maman.
+maman|Tu l'entends, Nino ?
+narrateur|Nino écoute la goutte, un instant.
+narrateur|La grille du jardin grince, un peu.
+maman|On rentre.
+narrateur|Nino entre.
+narrateur|Il retire le manteau gris.
+narrateur|Il le raccroche au crochet.
+enfant-m|Il est à sa place.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>manteau,jardin,arrosoir</t>
         </is>
       </c>
     </row>
@@ -1784,17 +1791,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui.</t>
+          <t>On prend le sac, Nino ? Le pain, maintenant. Maman prend le sac vide. Nino va vers le crochet, seul. Il prend le manteau gris. Le manteau, maman. Tu l'as pris, toi. Ils traversent le jardin, puis la rue. Le fournil sent le chaud, si près. Je le prends ! Nino pousse la porte, trop vite. Le sac se coince dans le battant. Oh. Il veut foncer vers le pain chaud. Nino refuse de foncer. Attends, je regarde. Au-dessus du comptoir, un cadran brille. Un éclat d'horloge cligne sur la croûte. Comme à la cuisine ! Tu le vois, toi ? Oui, sur ce pain. Nino s'arrête, lent. Il écoute le fournil, un instant. Une pelle racle la pierre, plus loin. Le pain attend derrière le bois. On le prend ensemble ? Celui-là.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nino pose les chaussures. Le manteau reste au crochet. Maman pose le pain sur la planche. Tu as fini de poser tes chaussures ? Oui, maman. Le sac n'est plus vide. Les miettes nouvelles sentent le chaud. On a le pain, maintenant. Et le manteau est à sa place. Oui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;On prend le sac, Nino ? Le pain, maintenant. Maman prend le sac vide. Nino va vers le crochet, seul. Il prend le manteau gris. Le manteau, maman. Tu l'as pris, toi. Ils traversent le jardin, puis la rue. Le fournil sent le chaud, si près. Je le prends ! Nino pousse la porte, trop vite. Le sac se coince dans le battant. Oh. Il veut foncer vers le pain chaud. Nino refuse de foncer. Attends, je regarde. Au-dessus du comptoir, un cadran brille. Un &lt;emphasis level="moderate"&gt;éclat d'horloge&lt;/emphasis&gt; cligne sur la croûte. Comme à la cuisine ! Tu le vois, toi ? Oui, sur ce pain. Nino s'arrête, lent. Il écoute le fournil, un instant. Une pelle racle la pierre, plus loin. Le pain attend derrière le bois. On le prend ensemble ? Celui-là.&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Brice pose les chaussures. Le &lt;emphasis&gt;manteau&lt;/emphasis&gt; reste au crochet. [pause]</t>
+          <t>&lt;low-pitch&gt;On prend le sac, Nino ? Le pain, maintenant. Maman prend le sac vide. Nino va vers le crochet, seul. Il prend le manteau gris. Le manteau, maman. Tu l'as pris, toi. Ils traversent le jardin, puis la rue. Le fournil sent le chaud, si près. Je le prends ! Nino pousse la porte, trop vite. Le sac se coince dans le battant. Oh. Il veut foncer vers le pain chaud. Nino refuse de foncer. Attends, je regarde. Au-dessus du comptoir, un cadran brille. Un &lt;emphasis&gt;éclat d'horloge&lt;/emphasis&gt; cligne sur la croûte. Comme à la cuisine ! Tu le vois, toi ? Oui, sur ce pain. Nino s'arrête, lent. Il écoute le fournil, un instant. Une pelle racle la pierre, plus loin. Le pain attend derrière le bois. On le prend ensemble ? Celui-là.&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1841,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1849,22 +1856,26 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
+          <t>-2st</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>low-pitch</t>
+        </is>
+      </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>medium</t>
@@ -1875,30 +1886,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>manteau</t>
+          <t>éclat d'horloge</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>tense</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1907,33 +1918,59 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="AT5" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=obstacle; intention=alerter_sans_effrayer; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_retrouve_l_eclat; tempo=resserré; sourire=aucun; respiration=retenue</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino pose les chaussures.
-narrateur|Le manteau reste au crochet.
-narrateur|Maman pose le pain sur la planche.
-maman|Tu as fini de poser tes chaussures ?
-enfant-m|Oui, maman.
-narrateur|Le sac n'est plus vide.
-narrateur|Les miettes nouvelles sentent le chaud.
-maman|On a le pain, maintenant.
-enfant-m|Et le manteau est à sa place.
-maman|Oui.</t>
+          <t>maman|On prend le sac, Nino ?
+enfant-m|Le pain, maintenant.
+narrateur|Maman prend le sac vide.
+narrateur|Nino va vers le crochet, seul.
+narrateur|Il prend le manteau gris.
+enfant-m|Le manteau, maman.
+maman|Tu l'as pris, toi.
+narrateur|Ils traversent le jardin, puis la rue.
+narrateur|Le fournil sent le chaud, si près.
+enfant-m|Je le prends !
+narrateur|Nino pousse la porte, trop vite.
+narrateur|Le sac se coince dans le battant.
+enfant-m|Oh.
+narrateur|Il veut foncer vers le pain chaud.
+narrateur|Nino refuse de foncer.
+enfant-m|Attends, je regarde.
+narrateur|Au-dessus du comptoir, un cadran brille.
+narrateur|Un éclat d'horloge cligne sur la croûte.
+enfant-m|Comme à la cuisine !
+maman|Tu le vois, toi ?
+enfant-m|Oui, sur ce pain.
+narrateur|Nino s'arrête, lent.
+narrateur|Il écoute le fournil, un instant.
+narrateur|Une pelle racle la pierre, plus loin.
+narrateur|Le pain attend derrière le bois.
+maman|On le prend ensemble ?
+enfant-m|Celui-là.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte,fournil,pelle</t>
         </is>
       </c>
     </row>
@@ -1960,17 +1997,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Le pain doré attend sur la planche.</t>
+          <t>Maman glisse le pain dans le sac. Le lin se tend, un peu chaud. Il sent le fournil, maman. Tu le portes, toi ? Oui, contre moi. Nino serre le sac contre le manteau. Sur la croûte, l'éclat d'horloge reste. Comme sur le lin, maman. Tu le ramènes à la maison ? Oui. Ils rentrent par le jardin. Nino raccroche le manteau au crochet. Le sac repose sur la chaise. Il n'est plus vide. Tu as fini de poser le sac ? Oui, maman. L'éclat d'horloge laisse une trace claire, sur la croûte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai pris le manteau deux fois. Jardin, puis boulangerie. Et tu l'as raccroché. Bravo, Nino. Le pain doré attend sur la planche.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Maman glisse le pain dans le sac. Le lin se tend, un peu chaud. Il sent le fournil, maman. Tu le portes, toi ? Oui, contre moi. Nino serre le sac contre le manteau. Sur la croûte, l'&lt;emphasis level="moderate"&gt;éclat d'horloge&lt;/emphasis&gt; reste. Comme sur le lin, maman. Tu le ramènes à la maison ? Oui. Ils rentrent par le jardin. Nino raccroche le manteau au crochet. Le sac repose sur la chaise. Il n'est plus vide. Tu as fini de poser le sac ? Oui, maman. L'éclat d'horloge laisse une trace claire, sur la croûte.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Maman glisse le pain dans le sac. Le lin se tend, un peu chaud. Il sent le fournil, maman. Tu le portes, toi ? Oui, contre moi. Nino serre le sac contre le manteau. Sur la croûte, l'&lt;emphasis&gt;éclat d'horloge&lt;/emphasis&gt; reste. Comme sur le lin, maman. Tu le ramènes à la maison ? Oui. Ils rentrent par le jardin. Nino raccroche le manteau au crochet. Le sac repose sur la chaise. Il n'est plus vide. Tu as fini de poser le sac ? Oui, maman. L'éclat d'horloge laisse une trace claire, sur la croûte.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2017,15 +2054,15 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2037,12 +2074,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2051,17 +2088,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat d'horloge</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2070,11 +2111,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2083,28 +2124,49 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_cadran_est_sur_la_croute; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai pris le manteau deux fois.
-enfant-m|Jardin, puis boulangerie.
-maman|Et tu l'as raccroché.
-maman|Bravo, Nino.
-narrateur|Le pain doré attend sur la planche.</t>
+          <t>narrateur|Maman glisse le pain dans le sac.
+narrateur|Le lin se tend, un peu chaud.
+enfant-m|Il sent le fournil, maman.
+maman|Tu le portes, toi ?
+enfant-m|Oui, contre moi.
+narrateur|Nino serre le sac contre le manteau.
+narrateur|Sur la croûte, l'éclat d'horloge reste.
+enfant-m|Comme sur le lin, maman.
+maman|Tu le ramènes à la maison ?
+enfant-m|Oui.
+narrateur|Ils rentrent par le jardin.
+narrateur|Nino raccroche le manteau au crochet.
+narrateur|Le sac repose sur la chaise.
+enfant-m|Il n'est plus vide.
+maman|Tu as fini de poser le sac ?
+enfant-m|Oui, maman.
+narrateur|L'éclat d'horloge laisse une trace claire, sur la croûte.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>sac,crochet</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2217,6 +2279,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
